--- a/sheets/조재수대금교본/검수/천년바위.xlsx
+++ b/sheets/조재수대금교본/검수/천년바위.xlsx
@@ -2861,7 +2861,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -2870,27 +2870,15 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -2941,11 +2929,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -2965,11 +2949,7 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
@@ -3030,16 +3010,11 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -3064,8 +3039,7 @@
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -3078,8 +3052,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -3115,7 +3088,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南∽</t>
+南</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -3188,9 +3161,8 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
-–
-ﾉ</t>
+          <t xml:space="preserve">潢
+–</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3217,7 +3189,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -3285,23 +3257,11 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
@@ -3310,11 +3270,7 @@
         </is>
       </c>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
       <c r="N14" s="21"/>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/천년바위.xlsx
+++ b/sheets/조재수대금교본/검수/천년바위.xlsx
@@ -2861,7 +2861,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -2870,15 +2870,27 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
@@ -2929,7 +2941,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -2949,7 +2965,11 @@
         </is>
       </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="96.05" customHeight="true">
@@ -3088,7 +3108,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林潢
-南</t>
+南∽</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -3161,8 +3181,9 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-–</t>
+          <t xml:space="preserve">潢ʒ
+–
+ﾉ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -3189,7 +3210,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="Q11" s="24"/>

--- a/sheets/조재수대금교본/검수/천년바위.xlsx
+++ b/sheets/조재수대금교본/검수/천년바위.xlsx
@@ -2769,21 +2769,21 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
